--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:51</t>
+    <t xml:space="preserve">2026-09-09 22:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:39</t>
+    <t xml:space="preserve">2026-09-18 10:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:02</t>
+    <t xml:space="preserve">2026-09-23 12:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:07</t>
+    <t xml:space="preserve">2026-10-02 13:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Hualpén</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:36</t>
+    <t xml:space="preserve">2026-10-04 08:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:23</t>
+    <t xml:space="preserve">2026-10-05 08:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
